--- a/research/traditional_assets/database/data/germany/germany_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_restaurant_dining.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.805</v>
+        <v>0.652</v>
       </c>
       <c r="G2">
-        <v>-0.06812132082852319</v>
+        <v>0.005509594589955717</v>
       </c>
       <c r="H2">
-        <v>-0.1155772661788137</v>
+        <v>-0.03863581751398854</v>
       </c>
       <c r="I2">
-        <v>-0.1133447186894755</v>
+        <v>-0.05630599704781848</v>
       </c>
       <c r="J2">
-        <v>-0.1133447186894755</v>
+        <v>-0.05630599704781848</v>
       </c>
       <c r="K2">
-        <v>-2530.3</v>
+        <v>-2406.3</v>
       </c>
       <c r="L2">
-        <v>-0.2414108936868519</v>
+        <v>-0.2065068140468916</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0004387378231663485</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001471138262062087</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0004387378231663485</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.001471138262062087</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>2100.5</v>
+        <v>1881.4</v>
       </c>
       <c r="V2">
-        <v>0.2903448752505357</v>
+        <v>0.2331755199167142</v>
       </c>
       <c r="W2">
-        <v>-0.5394750868814362</v>
+        <v>-0.7254884225759769</v>
       </c>
       <c r="X2">
-        <v>0.1006189963782808</v>
+        <v>0.1014156585562877</v>
       </c>
       <c r="Y2">
-        <v>-0.640094083259717</v>
+        <v>-0.8269040811322647</v>
       </c>
       <c r="Z2">
-        <v>1.396277942077638</v>
+        <v>1.590228590924599</v>
       </c>
       <c r="AA2">
-        <v>-0.1582607305571097</v>
+        <v>-0.08953940634595701</v>
       </c>
       <c r="AB2">
-        <v>0.0837786139849294</v>
+        <v>0.08504320894835282</v>
       </c>
       <c r="AC2">
-        <v>-0.2420393445420391</v>
+        <v>-0.1745826152943099</v>
       </c>
       <c r="AD2">
-        <v>6111.2</v>
+        <v>5992.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6111.2</v>
+        <v>5992.9</v>
       </c>
       <c r="AG2">
-        <v>4010.7</v>
+        <v>4111.5</v>
       </c>
       <c r="AH2">
-        <v>0.4579152835744846</v>
+        <v>0.4261920847704725</v>
       </c>
       <c r="AI2">
-        <v>0.6484238225089393</v>
+        <v>0.8179423486378774</v>
       </c>
       <c r="AJ2">
-        <v>0.3566588411055383</v>
+        <v>0.3375588049359201</v>
       </c>
       <c r="AK2">
-        <v>0.5475956418448431</v>
+        <v>0.7550409519961803</v>
       </c>
       <c r="AL2">
-        <v>338.4</v>
+        <v>331.5</v>
       </c>
       <c r="AM2">
-        <v>260.9</v>
+        <v>197.4</v>
       </c>
       <c r="AN2">
-        <v>-7.083806653529615</v>
+        <v>-15.10307459677419</v>
       </c>
       <c r="AO2">
-        <v>-3.510638297872341</v>
+        <v>-1.979185520361991</v>
       </c>
       <c r="AP2">
-        <v>-4.649008925466558</v>
+        <v>-10.36164314516129</v>
       </c>
       <c r="AQ2">
-        <v>-4.553468761977769</v>
+        <v>-3.32370820668693</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.805</v>
+        <v>0.652</v>
       </c>
       <c r="G3">
-        <v>-0.06812132082852319</v>
+        <v>0.005509594589955717</v>
       </c>
       <c r="H3">
-        <v>-0.1155772661788137</v>
+        <v>-0.03863581751398854</v>
       </c>
       <c r="I3">
-        <v>-0.1133447186894755</v>
+        <v>-0.05630599704781848</v>
       </c>
       <c r="J3">
-        <v>-0.1133447186894755</v>
+        <v>-0.05630599704781848</v>
       </c>
       <c r="K3">
-        <v>-2530.3</v>
+        <v>-2406.3</v>
       </c>
       <c r="L3">
-        <v>-0.2414108936868519</v>
+        <v>-0.2065068140468916</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.54</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0004387378231663485</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.001471138262062087</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.54</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0004387378231663485</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.001471138262062087</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2100.5</v>
+        <v>1881.4</v>
       </c>
       <c r="V3">
-        <v>0.2903448752505357</v>
+        <v>0.2331755199167142</v>
       </c>
       <c r="W3">
-        <v>-0.5394750868814362</v>
+        <v>-0.7254884225759769</v>
       </c>
       <c r="X3">
-        <v>0.1006189963782808</v>
+        <v>0.1014156585562877</v>
       </c>
       <c r="Y3">
-        <v>-0.640094083259717</v>
+        <v>-0.8269040811322647</v>
       </c>
       <c r="Z3">
-        <v>1.396277942077638</v>
+        <v>1.590228590924599</v>
       </c>
       <c r="AA3">
-        <v>-0.1582607305571097</v>
+        <v>-0.08953940634595701</v>
       </c>
       <c r="AB3">
-        <v>0.0837786139849294</v>
+        <v>0.08504320894835282</v>
       </c>
       <c r="AC3">
-        <v>-0.2420393445420391</v>
+        <v>-0.1745826152943099</v>
       </c>
       <c r="AD3">
-        <v>6111.2</v>
+        <v>5992.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6111.2</v>
+        <v>5992.9</v>
       </c>
       <c r="AG3">
-        <v>4010.7</v>
+        <v>4111.5</v>
       </c>
       <c r="AH3">
-        <v>0.4579152835744846</v>
+        <v>0.4261920847704725</v>
       </c>
       <c r="AI3">
-        <v>0.6484238225089393</v>
+        <v>0.8179423486378774</v>
       </c>
       <c r="AJ3">
-        <v>0.3566588411055383</v>
+        <v>0.3375588049359201</v>
       </c>
       <c r="AK3">
-        <v>0.5475956418448431</v>
+        <v>0.7550409519961803</v>
       </c>
       <c r="AL3">
-        <v>338.4</v>
+        <v>331.5</v>
       </c>
       <c r="AM3">
-        <v>260.9</v>
+        <v>197.4</v>
       </c>
       <c r="AN3">
-        <v>-7.083806653529615</v>
+        <v>-15.10307459677419</v>
       </c>
       <c r="AO3">
-        <v>-3.510638297872341</v>
+        <v>-1.979185520361991</v>
       </c>
       <c r="AP3">
-        <v>-4.649008925466558</v>
+        <v>-10.36164314516129</v>
       </c>
       <c r="AQ3">
-        <v>-4.553468761977769</v>
+        <v>-3.32370820668693</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_restaurant_dining.xlsx
@@ -642,10 +642,10 @@
         <v>-0.7254884225759769</v>
       </c>
       <c r="X2">
-        <v>0.1014156585562877</v>
+        <v>0.1013799026326538</v>
       </c>
       <c r="Y2">
-        <v>-0.8269040811322647</v>
+        <v>-0.8268683252086306</v>
       </c>
       <c r="Z2">
         <v>1.590228590924599</v>
@@ -654,10 +654,10 @@
         <v>-0.08953940634595701</v>
       </c>
       <c r="AB2">
-        <v>0.08504320894835282</v>
+        <v>0.08502269191635531</v>
       </c>
       <c r="AC2">
-        <v>-0.1745826152943099</v>
+        <v>-0.1745620982623123</v>
       </c>
       <c r="AD2">
         <v>5992.9</v>
@@ -773,10 +773,10 @@
         <v>-0.7254884225759769</v>
       </c>
       <c r="X3">
-        <v>0.1014156585562877</v>
+        <v>0.1013799026326538</v>
       </c>
       <c r="Y3">
-        <v>-0.8269040811322647</v>
+        <v>-0.8268683252086306</v>
       </c>
       <c r="Z3">
         <v>1.590228590924599</v>
@@ -785,10 +785,10 @@
         <v>-0.08953940634595701</v>
       </c>
       <c r="AB3">
-        <v>0.08504320894835282</v>
+        <v>0.08502269191635531</v>
       </c>
       <c r="AC3">
-        <v>-0.1745826152943099</v>
+        <v>-0.1745620982623123</v>
       </c>
       <c r="AD3">
         <v>5992.9</v>
